--- a/data/trans_dic/P19C10_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,16</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,82</t>
+          <t>0,05; 0,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,75</t>
+          <t>0,38; 2,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,47</t>
+          <t>0,2; 1,46</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,07</t>
+          <t>0,06; 0,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,56</t>
+          <t>0,05; 0,78</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,45</t>
+          <t>0,44; 2,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,59</t>
+          <t>0,3; 1,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,62</t>
+          <t>0,5; 1,61</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,47</t>
+          <t>0,32; 1,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,95</t>
+          <t>0,16; 0,85</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,57</t>
+          <t>0,15; 0,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,82</t>
+          <t>0,38; 0,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,62</t>
+          <t>0,31; 0,6</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1844</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>159; 3329</t>
+          <t>0; 3671</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4146</t>
+          <t>0; 2796</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7073</t>
+          <t>0; 6892</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4035</t>
+          <t>0; 4111</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>544; 8297</t>
+          <t>551; 7697</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1671</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1244; 9235</t>
+          <t>1269; 9042</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1247; 9376</t>
+          <t>1263; 9285</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>350; 5057</t>
+          <t>304; 4548</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>327; 4403</t>
+          <t>359; 6091</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2425</t>
+          <t>0; 2214</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1412</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1902</t>
+          <t>0; 1595</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1896</t>
+          <t>0; 1716</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2575; 14695</t>
+          <t>2617; 14857</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2423; 13177</t>
+          <t>2486; 12787</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7248; 23099</t>
+          <t>7149; 22920</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 9399</t>
+          <t>0; 7890</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2202; 10364</t>
+          <t>2235; 10408</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2771; 15242</t>
+          <t>2649; 13699</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4182; 18953</t>
+          <t>5032; 19801</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13197; 29381</t>
+          <t>13498; 28889</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20987; 42989</t>
+          <t>21345; 41908</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C10_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,47</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,76</t>
+          <t>0,06; 0,82</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,7</t>
+          <t>0,38; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,46</t>
+          <t>0,19; 1,53</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,96</t>
+          <t>0,08; 1,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,78</t>
+          <t>0,04; 0,66</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,48</t>
+          <t>0,35; 2,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,54</t>
+          <t>0,62; 2,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,61</t>
+          <t>0,65; 1,71</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,48</t>
+          <t>0,31; 1,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,85</t>
+          <t>0,2; 0,96</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,59</t>
+          <t>0,15; 0,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,81</t>
+          <t>0,43; 0,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,6</t>
+          <t>0,35; 0,66</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>0; 3023</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2796</t>
+          <t>0; 3515</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2546</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6892</t>
+          <t>0; 6122</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>551; 7697</t>
+          <t>587; 8608</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1269; 9042</t>
+          <t>1289; 9001</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1263; 9285</t>
+          <t>1247; 9819</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1735</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>304; 4548</t>
+          <t>331; 4943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>359; 6091</t>
+          <t>339; 5210</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>500</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2634</t>
+          <t>0; 2439</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2214</t>
+          <t>0; 2501</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1595</t>
+          <t>0; 1906</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1716</t>
+          <t>0; 2331</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>16164</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2617; 14857</t>
+          <t>2427; 14596</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2486; 12787</t>
+          <t>4617; 14990</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7149; 22920</t>
+          <t>9365; 24660</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7674</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 7890</t>
+          <t>0; 9802</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2235; 10408</t>
+          <t>2497; 11841</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2649; 13699</t>
+          <t>3227; 15179</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5032; 19801</t>
+          <t>5019; 20541</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13498; 28889</t>
+          <t>15731; 33037</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21345; 41908</t>
+          <t>24385; 46626</t>
         </is>
       </c>
     </row>
